--- a/site/leagues/proliga/2026_2027/xlsx/team_packs/team_pack_SLB.xlsx
+++ b/site/leagues/proliga/2026_2027/xlsx/team_packs/team_pack_SLB.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$B$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'rotation'!$A$1:$U$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'rotation'!$A$1:$U$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'key_lineups'!$A$1:$L$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'duos_trios'!$A$1:$J$7</definedName>
   </definedNames>
@@ -472,7 +472,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>S. Sousa (15.5 ppg)</t>
+          <t>S. Sousa (15.7 ppg)</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>S. Sousa (34.5 mpg)</t>
+          <t>S. Sousa (35.4 mpg)</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>M. Sousa (62.5%)</t>
+          <t>M. Sousa (45.5%)</t>
         </is>
       </c>
     </row>
@@ -520,7 +520,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>J. Mendes | K. Domingues | M. Sousa | S. Sousa | T. Filipe (24.0 min)</t>
+          <t>J. Mendes | K. Domingues | M. Sousa | S. Sousa | T. Filipe (29.1 min)</t>
         </is>
       </c>
     </row>
@@ -532,7 +532,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>J. Mendes | K. Domingues | M. Sousa | S. Sousa | T. Filipe (5.0 net)</t>
+          <t>K. Domingues | M. Sousa | S. Sousa | T. Filipe | W. Oliveira (28.5 net)</t>
         </is>
       </c>
     </row>
@@ -544,7 +544,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>K. Domingues | S. Sousa (-10.3 net)</t>
+          <t>S. Sousa | T. Filipe (9.3 net)</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>J. Mendes | K. Domingues | S. Sousa (-13.4 net)</t>
+          <t>K. Domingues | M. Sousa | S. Sousa (6.2 net)</t>
         </is>
       </c>
     </row>
@@ -572,7 +572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U6"/>
+  <dimension ref="A1:U7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -595,7 +595,7 @@
     <col width="10" customWidth="1" min="18" max="18"/>
     <col width="15" customWidth="1" min="19" max="19"/>
     <col width="23" customWidth="1" min="20" max="20"/>
-    <col width="41" customWidth="1" min="21" max="21"/>
+    <col width="38" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -722,28 +722,28 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>69.09999999999999</v>
+        <v>106.2</v>
       </c>
       <c r="G2" t="n">
-        <v>34.5</v>
+        <v>35.4</v>
       </c>
       <c r="H2" t="n">
-        <v>15.5</v>
+        <v>15.7</v>
       </c>
       <c r="I2" t="n">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="K2" t="n">
-        <v>4.5</v>
+        <v>5.7</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -753,12 +753,12 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -768,19 +768,19 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>51.3%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>-1.5</v>
+        <v>0.7</v>
       </c>
       <c r="T2" t="n">
-        <v>49.1</v>
+        <v>49.6</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -796,78 +796,78 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>K. Domingues</t>
+          <t>T. Filipe</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>62.4</v>
+        <v>92.8</v>
       </c>
       <c r="G3" t="n">
-        <v>31.2</v>
+        <v>30.9</v>
       </c>
       <c r="H3" t="n">
+        <v>11</v>
+      </c>
+      <c r="I3" t="n">
         <v>7</v>
       </c>
-      <c r="I3" t="n">
-        <v>4.5</v>
-      </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="K3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L3" t="n">
         <v>1</v>
       </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>-11.5</v>
+        <v>-0.3</v>
       </c>
       <c r="T3" t="n">
-        <v>-23.2</v>
+        <v>27.3</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>high-minutes</t>
+          <t>high-minutes, impact</t>
         </is>
       </c>
     </row>
@@ -879,78 +879,78 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>M. Sousa</t>
+          <t>K. Domingues</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" t="n">
+        <v>88.40000000000001</v>
+      </c>
+      <c r="G4" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="H4" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="I4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J4" t="n">
         <v>2</v>
       </c>
-      <c r="E4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F4" t="n">
-        <v>59.8</v>
-      </c>
-      <c r="G4" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="H4" t="n">
-        <v>13</v>
-      </c>
-      <c r="I4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3</v>
-      </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>0.7</v>
       </c>
       <c r="L4" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>86.4%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>84.4%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>-3.5</v>
+        <v>-3.7</v>
       </c>
       <c r="T4" t="n">
-        <v>11.8</v>
+        <v>1.3</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>high-minutes, primary-scorer, efficient</t>
+          <t>high-minutes</t>
         </is>
       </c>
     </row>
@@ -962,78 +962,78 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>J. Mendes</t>
+          <t>M. Sousa</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>G</t>
         </is>
       </c>
       <c r="D5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" t="n">
+        <v>87.2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>11</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K5" t="n">
         <v>2</v>
       </c>
-      <c r="E5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F5" t="n">
-        <v>59.8</v>
-      </c>
-      <c r="G5" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="H5" t="n">
-        <v>10</v>
-      </c>
-      <c r="I5" t="n">
-        <v>3</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1.5</v>
-      </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>50.6%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>-11</v>
+        <v>1.3</v>
       </c>
       <c r="T5" t="n">
-        <v>-20</v>
+        <v>22.9</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>high-minutes</t>
+          <t>high-minutes, efficient, shooter</t>
         </is>
       </c>
     </row>
@@ -1045,7 +1045,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>T. Filipe</t>
+          <t>J. Mendes</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1054,74 +1054,157 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
         <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>59</v>
+        <v>83.8</v>
       </c>
       <c r="G6" t="n">
-        <v>29.5</v>
+        <v>27.9</v>
       </c>
       <c r="H6" t="n">
-        <v>9</v>
+        <v>10.3</v>
       </c>
       <c r="I6" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>38.5%</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>48.1%</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>52.5%</t>
+        </is>
+      </c>
+      <c r="S6" t="n">
+        <v>-11</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-29.8</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>high-minutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SL Benfica</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>W. Oliveira</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>58.9</v>
+      </c>
+      <c r="G7" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="H7" t="n">
         <v>6</v>
       </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>30.0%</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>14.3%</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>55.6%</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>32.5%</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>37.6%</t>
-        </is>
-      </c>
-      <c r="S6" t="n">
-        <v>-3</v>
-      </c>
-      <c r="T6" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>high-minutes, impact</t>
+      <c r="I7" t="n">
+        <v>8</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>31.6%</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>31.6%</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>35.2%</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>rotation</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U6"/>
+  <autoFilter ref="A1:U7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1228,31 +1311,31 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>24</v>
+        <v>29.1</v>
       </c>
       <c r="G2" t="n">
-        <v>83.3</v>
+        <v>85.3</v>
       </c>
       <c r="H2" t="n">
-        <v>78.3</v>
+        <v>71.5</v>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>13.8</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L2" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3">
@@ -1268,7 +1351,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>J. Mendes | K. Domingues | M. Sousa | S. Sousa | T. Filipe</t>
+          <t>K. Domingues | M. Sousa | S. Sousa | T. Filipe | W. Oliveira</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -1278,25 +1361,25 @@
         <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>24</v>
+        <v>15.4</v>
       </c>
       <c r="G3" t="n">
-        <v>83.3</v>
+        <v>59.5</v>
       </c>
       <c r="H3" t="n">
-        <v>78.3</v>
+        <v>31.1</v>
       </c>
       <c r="I3" t="n">
-        <v>5</v>
+        <v>28.5</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L3" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
@@ -1312,7 +1395,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>J. Mendes | K. Domingues | M. Sousa | S. Sousa | T. Filipe</t>
+          <t>K. Domingues | M. Sousa | S. Sousa | T. Filipe | W. Oliveira</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -1322,25 +1405,25 @@
         <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>24</v>
+        <v>15.4</v>
       </c>
       <c r="G4" t="n">
-        <v>83.3</v>
+        <v>59.5</v>
       </c>
       <c r="H4" t="n">
-        <v>78.3</v>
+        <v>31.1</v>
       </c>
       <c r="I4" t="n">
-        <v>5</v>
+        <v>28.5</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L4" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -1440,26 +1523,26 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>K. Domingues | S. Sousa</t>
+          <t>S. Sousa | T. Filipe</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="G2" t="n">
-        <v>54.3</v>
+        <v>81.8</v>
       </c>
       <c r="H2" t="n">
-        <v>55.3</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>65.59999999999999</v>
+        <v>62.1</v>
       </c>
       <c r="J2" t="n">
-        <v>-10.3</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -1484,22 +1567,22 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="G3" t="n">
-        <v>50.9</v>
+        <v>81.8</v>
       </c>
       <c r="H3" t="n">
-        <v>71.5</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>64.40000000000001</v>
+        <v>62.1</v>
       </c>
       <c r="J3" t="n">
-        <v>7.1</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -1520,26 +1603,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>S. Sousa | T. Filipe</t>
+          <t>M. Sousa | S. Sousa</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G4" t="n">
-        <v>50.9</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>71.5</v>
+        <v>66.8</v>
       </c>
       <c r="I4" t="n">
-        <v>64.40000000000001</v>
+        <v>60.2</v>
       </c>
       <c r="J4" t="n">
-        <v>7.1</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="5">
@@ -1560,26 +1643,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>J. Mendes | K. Domingues | S. Sousa</t>
+          <t>K. Domingues | M. Sousa | S. Sousa</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G5" t="n">
-        <v>44.9</v>
+        <v>65</v>
       </c>
       <c r="H5" t="n">
-        <v>58.8</v>
+        <v>65.3</v>
       </c>
       <c r="I5" t="n">
-        <v>72.2</v>
+        <v>59.1</v>
       </c>
       <c r="J5" t="n">
-        <v>-13.4</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="6">
@@ -1604,22 +1687,22 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G6" t="n">
-        <v>38.5</v>
+        <v>61.6</v>
       </c>
       <c r="H6" t="n">
-        <v>73.8</v>
+        <v>75.3</v>
       </c>
       <c r="I6" t="n">
-        <v>65.5</v>
+        <v>59.7</v>
       </c>
       <c r="J6" t="n">
-        <v>8.300000000000001</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="7">
@@ -1640,26 +1723,26 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>M. Sousa | S. Sousa | T. Filipe</t>
+          <t>K. Domingues | S. Sousa | T. Filipe</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G7" t="n">
-        <v>38.5</v>
+        <v>59.6</v>
       </c>
       <c r="H7" t="n">
-        <v>73.8</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>65.5</v>
+        <v>58.4</v>
       </c>
       <c r="J7" t="n">
-        <v>8.300000000000001</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
   </sheetData>
